--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="20.33203125" customWidth="1" style="6" min="2" max="2"/>
@@ -798,12 +798,12 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Conf.SkillBindingInfos</t>
+          <t>Conf.PipelineInfos</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SkillBindingInfo</t>
+          <t>PipelineInfo</t>
         </is>
       </c>
       <c r="D11" s="0" t="b">
@@ -811,24 +811,24 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>SkillBindingInfo@SkillBindingData.xlsx</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Conf.SkillBindingInfo</t>
+          <t>PipelineInfo@PipelineData.xlsx</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Conf.PipelineInfo</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Conf.PipelineInfos</t>
+          <t>Conf.EffectInfos</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PipelineInfo</t>
+          <t>EffectInfo</t>
         </is>
       </c>
       <c r="D12" s="0" t="b">
@@ -836,60 +836,35 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>PipelineInfo@PipelineData.xlsx</t>
+          <t>EffectInfo@EffectData.xlsx</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Conf.PipelineInfo</t>
+          <t>Conf.EffectInfo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Conf.EffectInfos</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>EffectInfo</t>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Conf.EnemyInfos</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>EnemyInfo</t>
         </is>
       </c>
       <c r="D13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>EffectInfo@EffectData.xlsx</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Conf.EffectInfo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Conf.EnemyInfos</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>EnemyInfo</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>EnemyInfo@EnemyData.xlsx</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>Conf.EnemyInfo</t>
         </is>
@@ -904,9 +879,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
